--- a/artfynd/A 47276-2024 artfynd.xlsx
+++ b/artfynd/A 47276-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136678244</v>
       </c>
       <c r="B2" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47276-2024 artfynd.xlsx
+++ b/artfynd/A 47276-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136678244</v>
       </c>
       <c r="B2" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47276-2024 artfynd.xlsx
+++ b/artfynd/A 47276-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136678244</v>
       </c>
       <c r="B2" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47276-2024 artfynd.xlsx
+++ b/artfynd/A 47276-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136678244</v>
       </c>
       <c r="B2" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47276-2024 artfynd.xlsx
+++ b/artfynd/A 47276-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136678244</v>
       </c>
       <c r="B2" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47276-2024 artfynd.xlsx
+++ b/artfynd/A 47276-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136678244</v>
       </c>
       <c r="B2" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47276-2024 artfynd.xlsx
+++ b/artfynd/A 47276-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136678244</v>
       </c>
       <c r="B2" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47276-2024 artfynd.xlsx
+++ b/artfynd/A 47276-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136678244</v>
       </c>
       <c r="B2" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47276-2024 artfynd.xlsx
+++ b/artfynd/A 47276-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136678244</v>
       </c>
       <c r="B2" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47276-2024 artfynd.xlsx
+++ b/artfynd/A 47276-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136678244</v>
       </c>
       <c r="B2" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47276-2024 artfynd.xlsx
+++ b/artfynd/A 47276-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136678244</v>
       </c>
       <c r="B2" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47276-2024 artfynd.xlsx
+++ b/artfynd/A 47276-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136678244</v>
       </c>
       <c r="B2" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47276-2024 artfynd.xlsx
+++ b/artfynd/A 47276-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136678244</v>
       </c>
       <c r="B2" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
